--- a/RACP Data/2018_RACP.xlsx
+++ b/RACP Data/2018_RACP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/linnmiller_pa_gov/Documents/Desktop/RACP Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/linnmiller_pa_gov/Documents/Desktop/racp_sector_classifer/RACP Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{B6A8BFCD-331B-4848-92AF-7D07415021A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07419D12-78D3-4646-9D00-C44D4C8AEA70}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RACP Awards 2018" sheetId="2" r:id="rId1"/>
@@ -5562,10 +5562,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5866,19 +5862,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72A1161-2031-44F0-859E-71266B5A9C86}">
   <dimension ref="A1:I507"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="4" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="28.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="100.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="4" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="4" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="28.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="100.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30"/>
       <c r="B1" s="5"/>
       <c r="C1" s="37" t="s">
@@ -5891,7 +5887,7 @@
       <c r="H1" s="37"/>
       <c r="I1" s="37"/>
     </row>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30"/>
       <c r="B2" s="5"/>
       <c r="C2" s="38" t="s">
@@ -5904,7 +5900,7 @@
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
     </row>
-    <row r="3" spans="1:9" s="6" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="6" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
       <c r="B3" s="5"/>
       <c r="C3" s="39" t="s">
@@ -5917,7 +5913,7 @@
       <c r="H3" s="39"/>
       <c r="I3" s="39"/>
     </row>
-    <row r="4" spans="1:9" s="9" customFormat="1" ht="50.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="9" customFormat="1" ht="50.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>0</v>
       </c>
@@ -5946,7 +5942,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>201802270751</v>
       </c>
@@ -5971,7 +5967,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>201802271014</v>
       </c>
@@ -5996,7 +5992,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>201802270680</v>
       </c>
@@ -6023,7 +6019,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>201802270947</v>
       </c>
@@ -6048,7 +6044,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>201802270765</v>
       </c>
@@ -6073,7 +6069,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>201802271060</v>
       </c>
@@ -6100,7 +6096,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>201802260626</v>
       </c>
@@ -6127,7 +6123,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>201802270792</v>
       </c>
@@ -6152,7 +6148,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>201802260487</v>
       </c>
@@ -6177,7 +6173,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>201802250391</v>
       </c>
@@ -6204,7 +6200,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>201802271043</v>
       </c>
@@ -6229,7 +6225,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>201802270921</v>
       </c>
@@ -6256,7 +6252,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>201802270972</v>
       </c>
@@ -6283,7 +6279,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>201802271033</v>
       </c>
@@ -6310,7 +6306,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>201802271039</v>
       </c>
@@ -6337,7 +6333,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>201802260529</v>
       </c>
@@ -6362,7 +6358,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>201802220223</v>
       </c>
@@ -6387,7 +6383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>201802270861</v>
       </c>
@@ -6414,7 +6410,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>201802260620</v>
       </c>
@@ -6439,7 +6435,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>201802260485</v>
       </c>
@@ -6466,7 +6462,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>201802220210</v>
       </c>
@@ -6491,7 +6487,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>201802271032</v>
       </c>
@@ -6518,7 +6514,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>201802270637</v>
       </c>
@@ -6545,7 +6541,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>201802271061</v>
       </c>
@@ -6572,7 +6568,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>201802270968</v>
       </c>
@@ -6599,7 +6595,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>201802270834</v>
       </c>
@@ -6624,7 +6620,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>201802271022</v>
       </c>
@@ -6651,7 +6647,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>201802210144</v>
       </c>
@@ -6676,7 +6672,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>201802270660</v>
       </c>
@@ -6701,7 +6697,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>201802270671</v>
       </c>
@@ -6728,7 +6724,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>201802260527</v>
       </c>
@@ -6755,7 +6751,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>201802260523</v>
       </c>
@@ -6784,7 +6780,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>201802270769</v>
       </c>
@@ -6811,7 +6807,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>201802270795</v>
       </c>
@@ -6836,7 +6832,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>201802230314</v>
       </c>
@@ -6863,7 +6859,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A40" s="14">
         <v>201802270683</v>
       </c>
@@ -6890,7 +6886,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
         <v>201802250402</v>
       </c>
@@ -6915,7 +6911,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>201802270824</v>
       </c>
@@ -6940,7 +6936,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>201802270822</v>
       </c>
@@ -6967,7 +6963,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>201802260568</v>
       </c>
@@ -6992,7 +6988,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>201802220178</v>
       </c>
@@ -7017,7 +7013,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>201802270633</v>
       </c>
@@ -7042,7 +7038,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>201802271017</v>
       </c>
@@ -7069,7 +7065,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>201802271053</v>
       </c>
@@ -7094,7 +7090,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
         <v>201802270970</v>
       </c>
@@ -7119,7 +7115,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A50" s="14">
         <v>201802270980</v>
       </c>
@@ -7146,7 +7142,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>201802270662</v>
       </c>
@@ -7173,7 +7169,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>201802260528</v>
       </c>
@@ -7198,7 +7194,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>201802270847</v>
       </c>
@@ -7223,7 +7219,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A54" s="14">
         <v>201802271015</v>
       </c>
@@ -7248,7 +7244,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>201802270881</v>
       </c>
@@ -7275,7 +7271,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>201802260510</v>
       </c>
@@ -7302,7 +7298,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>201802260572</v>
       </c>
@@ -7329,7 +7325,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>201802270811</v>
       </c>
@@ -7354,7 +7350,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>201802270871</v>
       </c>
@@ -7379,7 +7375,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>201802270870</v>
       </c>
@@ -7404,7 +7400,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>201801299708</v>
       </c>
@@ -7431,7 +7427,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>201802270963</v>
       </c>
@@ -7456,7 +7452,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>201802260518</v>
       </c>
@@ -7481,7 +7477,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>201802270835</v>
       </c>
@@ -7506,7 +7502,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>201802150017</v>
       </c>
@@ -7533,7 +7529,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>201802190055</v>
       </c>
@@ -7560,7 +7556,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>201802270752</v>
       </c>
@@ -7585,7 +7581,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>201802270863</v>
       </c>
@@ -7610,7 +7606,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>201802270839</v>
       </c>
@@ -7635,7 +7631,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>201802260571</v>
       </c>
@@ -7660,7 +7656,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>201802270975</v>
       </c>
@@ -7687,7 +7683,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
         <v>201802230368</v>
       </c>
@@ -7714,7 +7710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A73" s="14">
         <v>201802270957</v>
       </c>
@@ -7741,7 +7737,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A74" s="14">
         <v>201802210131</v>
       </c>
@@ -7766,7 +7762,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>201802270657</v>
       </c>
@@ -7791,7 +7787,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>201802220191</v>
       </c>
@@ -7816,7 +7812,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A77" s="14">
         <v>201802270865</v>
       </c>
@@ -7841,7 +7837,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
         <v>201802220197</v>
       </c>
@@ -7866,7 +7862,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>201802270757</v>
       </c>
@@ -7893,7 +7889,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>201802270766</v>
       </c>
@@ -7922,7 +7918,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A81" s="14">
         <v>201802270895</v>
       </c>
@@ -7949,7 +7945,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A82" s="14">
         <v>201802271049</v>
       </c>
@@ -7974,7 +7970,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A83" s="14">
         <v>201802270950</v>
       </c>
@@ -7999,7 +7995,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A84" s="14">
         <v>201802220215</v>
       </c>
@@ -8026,7 +8022,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A85" s="14">
         <v>201802271029</v>
       </c>
@@ -8051,7 +8047,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A86" s="14">
         <v>201802270907</v>
       </c>
@@ -8078,7 +8074,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A87" s="14">
         <v>201802270856</v>
       </c>
@@ -8105,7 +8101,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="14">
         <v>201802260494</v>
       </c>
@@ -8130,7 +8126,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A89" s="14">
         <v>201802260496</v>
       </c>
@@ -8155,7 +8151,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A90" s="14">
         <v>201802260497</v>
       </c>
@@ -8180,7 +8176,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A91" s="14">
         <v>201802230343</v>
       </c>
@@ -8207,7 +8203,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A92" s="14">
         <v>201802270985</v>
       </c>
@@ -8232,7 +8228,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="14">
         <v>201802260598</v>
       </c>
@@ -8259,7 +8255,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A94" s="14">
         <v>201802260584</v>
       </c>
@@ -8284,7 +8280,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A95" s="14">
         <v>201802149996</v>
       </c>
@@ -8311,7 +8307,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A96" s="14">
         <v>201802220173</v>
       </c>
@@ -8336,7 +8332,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A97" s="14">
         <v>201802270855</v>
       </c>
@@ -8361,7 +8357,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A98" s="14">
         <v>201802220218</v>
       </c>
@@ -8390,7 +8386,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A99" s="14">
         <v>201802210130</v>
       </c>
@@ -8415,7 +8411,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A100" s="14">
         <v>201802270990</v>
       </c>
@@ -8440,7 +8436,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A101" s="14">
         <v>201802260612</v>
       </c>
@@ -8465,7 +8461,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A102" s="14">
         <v>201802270718</v>
       </c>
@@ -8490,7 +8486,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A103" s="14">
         <v>201802270831</v>
       </c>
@@ -8517,7 +8513,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A104" s="14">
         <v>201802270816</v>
       </c>
@@ -8544,7 +8540,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A105" s="14">
         <v>201802270984</v>
       </c>
@@ -8569,7 +8565,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A106" s="14">
         <v>201802260608</v>
       </c>
@@ -8594,7 +8590,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A107" s="14">
         <v>201802270805</v>
       </c>
@@ -8619,7 +8615,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="14">
         <v>201802271051</v>
       </c>
@@ -8644,7 +8640,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A109" s="14">
         <v>201802271050</v>
       </c>
@@ -8669,7 +8665,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A110" s="14">
         <v>201802230293</v>
       </c>
@@ -8696,7 +8692,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A111" s="14">
         <v>201802270996</v>
       </c>
@@ -8721,7 +8717,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="14">
         <v>201802260421</v>
       </c>
@@ -8746,7 +8742,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A113" s="14">
         <v>201802270986</v>
       </c>
@@ -8773,7 +8769,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A114" s="14">
         <v>201802270991</v>
       </c>
@@ -8800,7 +8796,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A115" s="14">
         <v>201802250399</v>
       </c>
@@ -8827,7 +8823,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A116" s="14">
         <v>201802270716</v>
       </c>
@@ -8852,7 +8848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
         <v>201802270988</v>
       </c>
@@ -8879,7 +8875,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
         <v>201802210132</v>
       </c>
@@ -8904,7 +8900,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A119" s="14">
         <v>201802270888</v>
       </c>
@@ -8929,7 +8925,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A120" s="14">
         <v>201802260427</v>
       </c>
@@ -8954,7 +8950,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A121" s="14">
         <v>201802260484</v>
       </c>
@@ -8979,7 +8975,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A122" s="14">
         <v>201802270891</v>
       </c>
@@ -9004,7 +9000,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A123" s="14">
         <v>201802270916</v>
       </c>
@@ -9029,7 +9025,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A124" s="14">
         <v>201802260446</v>
       </c>
@@ -9054,7 +9050,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A125" s="14">
         <v>201802270776</v>
       </c>
@@ -9081,7 +9077,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A126" s="14">
         <v>201802270843</v>
       </c>
@@ -9106,7 +9102,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A127" s="14">
         <v>201802260502</v>
       </c>
@@ -9131,7 +9127,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A128" s="14">
         <v>201802260594</v>
       </c>
@@ -9156,7 +9152,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A129" s="14">
         <v>201802230295</v>
       </c>
@@ -9181,7 +9177,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A130" s="14">
         <v>201802230269</v>
       </c>
@@ -9206,7 +9202,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A131" s="14">
         <v>201802260587</v>
       </c>
@@ -9231,7 +9227,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A132" s="14">
         <v>201802270929</v>
       </c>
@@ -9256,7 +9252,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A133" s="14">
         <v>201802260606</v>
       </c>
@@ -9281,7 +9277,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A134" s="14">
         <v>201802270987</v>
       </c>
@@ -9306,7 +9302,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A135" s="14">
         <v>201802270836</v>
       </c>
@@ -9331,7 +9327,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A136" s="14">
         <v>201802230319</v>
       </c>
@@ -9358,7 +9354,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A137" s="14">
         <v>201802271047</v>
       </c>
@@ -9383,7 +9379,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A138" s="14">
         <v>201802271002</v>
       </c>
@@ -9408,7 +9404,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A139" s="14">
         <v>201802260439</v>
       </c>
@@ -9433,7 +9429,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A140" s="14">
         <v>201802260438</v>
       </c>
@@ -9460,7 +9456,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
         <v>201802260524</v>
       </c>
@@ -9485,7 +9481,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
         <v>201802260425</v>
       </c>
@@ -9510,7 +9506,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A143" s="14">
         <v>201802260443</v>
       </c>
@@ -9537,7 +9533,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A144" s="14">
         <v>201802260615</v>
       </c>
@@ -9562,7 +9558,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A145" s="14">
         <v>201802270778</v>
       </c>
@@ -9587,7 +9583,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A146" s="14">
         <v>201802260457</v>
       </c>
@@ -9614,7 +9610,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A147" s="14">
         <v>201802260540</v>
       </c>
@@ -9641,7 +9637,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A148" s="14">
         <v>201802250401</v>
       </c>
@@ -9666,7 +9662,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A149" s="14">
         <v>201802260602</v>
       </c>
@@ -9693,7 +9689,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A150" s="14">
         <v>201802270777</v>
       </c>
@@ -9718,7 +9714,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A151" s="14">
         <v>201802260623</v>
       </c>
@@ -9745,7 +9741,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A152" s="14">
         <v>201802260451</v>
       </c>
@@ -9772,7 +9768,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A153" s="14">
         <v>201802200085</v>
       </c>
@@ -9799,7 +9795,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A154" s="14">
         <v>201802270999</v>
       </c>
@@ -9824,7 +9820,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A155" s="14">
         <v>201802260590</v>
       </c>
@@ -9851,7 +9847,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A156" s="14">
         <v>201802270956</v>
       </c>
@@ -9876,7 +9872,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A157" s="14">
         <v>201802270979</v>
       </c>
@@ -9901,7 +9897,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A158" s="14">
         <v>201802270962</v>
       </c>
@@ -9926,7 +9922,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A159" s="14">
         <v>201802271052</v>
       </c>
@@ -9951,7 +9947,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A160" s="14">
         <v>201802270704</v>
       </c>
@@ -9978,7 +9974,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A161" s="14">
         <v>201802270971</v>
       </c>
@@ -10003,7 +9999,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A162" s="14">
         <v>201802200104</v>
       </c>
@@ -10028,7 +10024,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A163" s="14">
         <v>201802270784</v>
       </c>
@@ -10053,7 +10049,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A164" s="14">
         <v>201802270845</v>
       </c>
@@ -10078,7 +10074,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A165" s="14">
         <v>201802260553</v>
       </c>
@@ -10103,7 +10099,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A166" s="14">
         <v>201802260610</v>
       </c>
@@ -10128,7 +10124,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A167" s="14">
         <v>201802270943</v>
       </c>
@@ -10155,7 +10151,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A168" s="14">
         <v>201802260501</v>
       </c>
@@ -10180,7 +10176,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A169" s="14">
         <v>201802270938</v>
       </c>
@@ -10205,7 +10201,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A170" s="14">
         <v>201802230370</v>
       </c>
@@ -10230,7 +10226,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A171" s="14">
         <v>201802260542</v>
       </c>
@@ -10255,7 +10251,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A172" s="14">
         <v>201802260533</v>
       </c>
@@ -10282,7 +10278,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A173" s="14">
         <v>201802270658</v>
       </c>
@@ -10307,7 +10303,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A174" s="14">
         <v>201802270901</v>
       </c>
@@ -10332,7 +10328,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A175" s="14">
         <v>201802270735</v>
       </c>
@@ -10357,7 +10353,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A176" s="14">
         <v>201802271025</v>
       </c>
@@ -10382,7 +10378,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A177" s="14">
         <v>201802260581</v>
       </c>
@@ -10409,7 +10405,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A178" s="14">
         <v>201802260585</v>
       </c>
@@ -10434,7 +10430,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A179" s="14">
         <v>201802260583</v>
       </c>
@@ -10463,7 +10459,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A180" s="14">
         <v>201802270714</v>
       </c>
@@ -10488,7 +10484,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A181" s="14">
         <v>201802230272</v>
       </c>
@@ -10513,7 +10509,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A182" s="14">
         <v>201802270890</v>
       </c>
@@ -10540,7 +10536,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A183" s="14">
         <v>201802270675</v>
       </c>
@@ -10565,7 +10561,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A184" s="14">
         <v>201802270733</v>
       </c>
@@ -10590,7 +10586,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A185" s="14">
         <v>201802260607</v>
       </c>
@@ -10615,7 +10611,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A186" s="14">
         <v>201802271030</v>
       </c>
@@ -10642,7 +10638,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A187" s="14">
         <v>201802270750</v>
       </c>
@@ -10667,7 +10663,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A188" s="14">
         <v>201802260554</v>
       </c>
@@ -10692,7 +10688,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A189" s="14">
         <v>201802271041</v>
       </c>
@@ -10717,7 +10713,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A190" s="14">
         <v>201802200080</v>
       </c>
@@ -10742,7 +10738,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A191" s="14">
         <v>201802271021</v>
       </c>
@@ -10767,7 +10763,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A192" s="14">
         <v>201802260618</v>
       </c>
@@ -10792,7 +10788,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A193" s="14">
         <v>201802270967</v>
       </c>
@@ -10819,7 +10815,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A194" s="14">
         <v>201802271008</v>
       </c>
@@ -10846,7 +10842,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A195" s="14">
         <v>201802260565</v>
       </c>
@@ -10871,7 +10867,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A196" s="14">
         <v>201802260470</v>
       </c>
@@ -10896,7 +10892,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A197" s="14">
         <v>201802149980</v>
       </c>
@@ -10923,7 +10919,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A198" s="14">
         <v>201802270978</v>
       </c>
@@ -10948,7 +10944,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A199" s="14">
         <v>201802260521</v>
       </c>
@@ -10973,7 +10969,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A200" s="14">
         <v>201802270696</v>
       </c>
@@ -10998,7 +10994,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A201" s="14">
         <v>201802270703</v>
       </c>
@@ -11023,7 +11019,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A202" s="14">
         <v>201802260423</v>
       </c>
@@ -11048,7 +11044,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A203" s="14">
         <v>201802270740</v>
       </c>
@@ -11075,7 +11071,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A204" s="14">
         <v>201802260481</v>
       </c>
@@ -11100,7 +11096,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A205" s="14">
         <v>201802270880</v>
       </c>
@@ -11125,7 +11121,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A206" s="14">
         <v>201802260453</v>
       </c>
@@ -11150,7 +11146,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A207" s="14">
         <v>201802260544</v>
       </c>
@@ -11175,7 +11171,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A208" s="14">
         <v>201802149993</v>
       </c>
@@ -11200,7 +11196,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A209" s="14">
         <v>201802270815</v>
       </c>
@@ -11227,7 +11223,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A210" s="14">
         <v>201802149991</v>
       </c>
@@ -11254,7 +11250,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A211" s="14">
         <v>201802220213</v>
       </c>
@@ -11279,7 +11275,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A212" s="14">
         <v>201802260498</v>
       </c>
@@ -11304,7 +11300,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A213" s="14">
         <v>201802149992</v>
       </c>
@@ -11329,7 +11325,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A214" s="14">
         <v>201802149988</v>
       </c>
@@ -11354,7 +11350,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A215" s="14">
         <v>201802220238</v>
       </c>
@@ -11381,7 +11377,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A216" s="14">
         <v>201802260628</v>
       </c>
@@ -11406,7 +11402,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A217" s="14">
         <v>201802149990</v>
       </c>
@@ -11431,7 +11427,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A218" s="14">
         <v>201802270661</v>
       </c>
@@ -11458,7 +11454,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A219" s="14">
         <v>201802260515</v>
       </c>
@@ -11483,7 +11479,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A220" s="14">
         <v>201802260621</v>
       </c>
@@ -11510,7 +11506,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A221" s="14">
         <v>201802270912</v>
       </c>
@@ -11535,7 +11531,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A222" s="14">
         <v>201802270747</v>
       </c>
@@ -11560,7 +11556,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A223" s="14">
         <v>201802260624</v>
       </c>
@@ -11587,7 +11583,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A224" s="14">
         <v>201802270754</v>
       </c>
@@ -11614,7 +11610,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A225" s="14">
         <v>201802270667</v>
       </c>
@@ -11639,7 +11635,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A226" s="14">
         <v>201802270842</v>
       </c>
@@ -11664,7 +11660,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A227" s="14">
         <v>201802270672</v>
       </c>
@@ -11689,7 +11685,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A228" s="14">
         <v>201802270722</v>
       </c>
@@ -11714,7 +11710,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A229" s="14">
         <v>201802270736</v>
       </c>
@@ -11741,7 +11737,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A230" s="14">
         <v>201802270844</v>
       </c>
@@ -11766,7 +11762,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A231" s="14">
         <v>201802260535</v>
       </c>
@@ -11793,7 +11789,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A232" s="14">
         <v>201802270700</v>
       </c>
@@ -11820,7 +11816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A233" s="14">
         <v>201802270771</v>
       </c>
@@ -11847,7 +11843,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A234" s="32">
         <v>201802271059</v>
       </c>
@@ -11872,7 +11868,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A235" s="32">
         <v>201802271055</v>
       </c>
@@ -11897,7 +11893,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A236" s="14">
         <v>201802260416</v>
       </c>
@@ -11922,7 +11918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A237" s="14">
         <v>201802260543</v>
       </c>
@@ -11949,7 +11945,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A238" s="14">
         <v>201802230252</v>
       </c>
@@ -11976,7 +11972,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A239" s="14">
         <v>201802270928</v>
       </c>
@@ -12001,7 +11997,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A240" s="14">
         <v>201802230294</v>
       </c>
@@ -12028,7 +12024,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A241" s="14">
         <v>201802220164</v>
       </c>
@@ -12055,7 +12051,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A242" s="14">
         <v>201802260588</v>
       </c>
@@ -12080,7 +12076,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A243" s="14">
         <v>201802260627</v>
       </c>
@@ -12107,7 +12103,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A244" s="14">
         <v>201802210140</v>
       </c>
@@ -12132,7 +12128,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A245" s="14">
         <v>201802270794</v>
       </c>
@@ -12157,7 +12153,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A246" s="14">
         <v>201802271040</v>
       </c>
@@ -12182,7 +12178,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A247" s="14">
         <v>201802220194</v>
       </c>
@@ -12209,7 +12205,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A248" s="14">
         <v>201802271028</v>
       </c>
@@ -12238,7 +12234,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A249" s="14">
         <v>201802270732</v>
       </c>
@@ -12267,7 +12263,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A250" s="14">
         <v>201802260514</v>
       </c>
@@ -12292,7 +12288,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A251" s="14">
         <v>201802270893</v>
       </c>
@@ -12317,7 +12313,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A252" s="14">
         <v>201802220165</v>
       </c>
@@ -12342,7 +12338,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A253" s="14">
         <v>201802270783</v>
       </c>
@@ -12367,7 +12363,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A254" s="14">
         <v>201802220242</v>
       </c>
@@ -12394,7 +12390,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A255" s="14">
         <v>201802270852</v>
       </c>
@@ -12421,7 +12417,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A256" s="14">
         <v>201802270955</v>
       </c>
@@ -12446,7 +12442,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A257" s="14">
         <v>201802260444</v>
       </c>
@@ -12471,7 +12467,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A258" s="14">
         <v>201802260561</v>
       </c>
@@ -12498,7 +12494,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A259" s="14">
         <v>201802260560</v>
       </c>
@@ -12525,7 +12521,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A260" s="14">
         <v>201802270868</v>
       </c>
@@ -12550,7 +12546,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A261" s="14">
         <v>201802270686</v>
       </c>
@@ -12575,7 +12571,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A262" s="14">
         <v>201802210123</v>
       </c>
@@ -12602,7 +12598,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A263" s="14">
         <v>201802270823</v>
       </c>
@@ -12627,7 +12623,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A264" s="14">
         <v>201802271034</v>
       </c>
@@ -12652,7 +12648,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A265" s="14">
         <v>201802260434</v>
       </c>
@@ -12677,7 +12673,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A266" s="14">
         <v>201802230328</v>
       </c>
@@ -12702,7 +12698,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A267" s="14">
         <v>201802270643</v>
       </c>
@@ -12727,7 +12723,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A268" s="14">
         <v>201802270920</v>
       </c>
@@ -12754,7 +12750,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A269" s="14">
         <v>201803061321</v>
       </c>
@@ -12779,7 +12775,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A270" s="14">
         <v>201802260600</v>
       </c>
@@ -12806,7 +12802,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A271" s="14">
         <v>201802270935</v>
       </c>
@@ -12831,7 +12827,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A272" s="14">
         <v>201802260483</v>
       </c>
@@ -12858,7 +12854,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A273" s="14">
         <v>201802220205</v>
       </c>
@@ -12885,7 +12881,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A274" s="14">
         <v>201802270682</v>
       </c>
@@ -12912,7 +12908,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A275" s="14">
         <v>201802250398</v>
       </c>
@@ -12939,7 +12935,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A276" s="14">
         <v>201802260569</v>
       </c>
@@ -12966,7 +12962,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A277" s="14">
         <v>201802270885</v>
       </c>
@@ -12991,7 +12987,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A278" s="14">
         <v>201802270876</v>
       </c>
@@ -13016,7 +13012,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A279" s="14">
         <v>201802270882</v>
       </c>
@@ -13041,7 +13037,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A280" s="14">
         <v>201802220202</v>
       </c>
@@ -13066,7 +13062,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A281" s="14">
         <v>201802270688</v>
       </c>
@@ -13091,7 +13087,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A282" s="14">
         <v>201802129949</v>
       </c>
@@ -13116,7 +13112,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A283" s="14">
         <v>201803061319</v>
       </c>
@@ -13141,7 +13137,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A284" s="14">
         <v>201802270712</v>
       </c>
@@ -13166,7 +13162,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A285" s="14">
         <v>201802200101</v>
       </c>
@@ -13193,7 +13189,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A286" s="14">
         <v>201802260426</v>
       </c>
@@ -13218,7 +13214,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A287" s="14">
         <v>201803061320</v>
       </c>
@@ -13245,7 +13241,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A288" s="14">
         <v>201802260564</v>
       </c>
@@ -13270,7 +13266,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A289" s="14">
         <v>201802270801</v>
       </c>
@@ -13295,7 +13291,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A290" s="14">
         <v>201802270819</v>
       </c>
@@ -13320,7 +13316,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A291" s="14">
         <v>201802270977</v>
       </c>
@@ -13347,7 +13343,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A292" s="14">
         <v>201802129948</v>
       </c>
@@ -13374,7 +13370,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A293" s="14">
         <v>201802270976</v>
       </c>
@@ -13401,7 +13397,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A294" s="14">
         <v>201802230264</v>
       </c>
@@ -13428,7 +13424,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A295" s="14">
         <v>201802230353</v>
       </c>
@@ -13455,7 +13451,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A296" s="14">
         <v>201802250395</v>
       </c>
@@ -13482,7 +13478,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A297" s="14">
         <v>201802230317</v>
       </c>
@@ -13507,7 +13503,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A298" s="14">
         <v>201802170051</v>
       </c>
@@ -13532,7 +13528,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A299" s="14">
         <v>201802260551</v>
       </c>
@@ -13557,7 +13553,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A300" s="14">
         <v>201802210147</v>
       </c>
@@ -13582,7 +13578,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A301" s="14">
         <v>201802230360</v>
       </c>
@@ -13607,7 +13603,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A302" s="14">
         <v>201802270702</v>
       </c>
@@ -13632,7 +13628,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A303" s="14">
         <v>201802270793</v>
       </c>
@@ -13657,7 +13653,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A304" s="14">
         <v>201802220229</v>
       </c>
@@ -13682,7 +13678,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A305" s="14">
         <v>201802260428</v>
       </c>
@@ -13709,7 +13705,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A306" s="14">
         <v>201802260563</v>
       </c>
@@ -13734,7 +13730,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A307" s="14">
         <v>201802260422</v>
       </c>
@@ -13759,7 +13755,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A308" s="14">
         <v>201802260557</v>
       </c>
@@ -13784,7 +13780,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A309" s="14">
         <v>201802270772</v>
       </c>
@@ -13809,7 +13805,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A310" s="14">
         <v>201802260576</v>
       </c>
@@ -13834,7 +13830,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A311" s="14">
         <v>201802260574</v>
       </c>
@@ -13859,7 +13855,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A312" s="14">
         <v>201802270908</v>
       </c>
@@ -13884,7 +13880,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A313" s="14">
         <v>201802260508</v>
       </c>
@@ -13911,7 +13907,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A314" s="14">
         <v>201802260532</v>
       </c>
@@ -13936,7 +13932,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A315" s="14">
         <v>201802260613</v>
       </c>
@@ -13961,7 +13957,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A316" s="14">
         <v>201802230349</v>
       </c>
@@ -13986,7 +13982,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A317" s="14">
         <v>201802271012</v>
       </c>
@@ -14011,7 +14007,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A318" s="14">
         <v>201802271013</v>
       </c>
@@ -14036,7 +14032,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A319" s="14">
         <v>201802149985</v>
       </c>
@@ -14063,7 +14059,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A320" s="14">
         <v>201802260465</v>
       </c>
@@ -14090,7 +14086,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A321" s="14">
         <v>201802270706</v>
       </c>
@@ -14115,7 +14111,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A322" s="14">
         <v>201802270940</v>
       </c>
@@ -14140,7 +14136,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A323" s="14">
         <v>201802260506</v>
       </c>
@@ -14167,7 +14163,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A324" s="14">
         <v>201802271031</v>
       </c>
@@ -14192,7 +14188,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A325" s="14">
         <v>201802270797</v>
       </c>
@@ -14217,7 +14213,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A326" s="14">
         <v>201802099925</v>
       </c>
@@ -14242,7 +14238,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A327" s="14">
         <v>201802271042</v>
       </c>
@@ -14267,7 +14263,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A328" s="14">
         <v>201802270760</v>
       </c>
@@ -14292,7 +14288,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A329" s="14">
         <v>201802270653</v>
       </c>
@@ -14317,7 +14313,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A330" s="14">
         <v>201802260520</v>
       </c>
@@ -14344,7 +14340,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A331" s="14">
         <v>201802270666</v>
       </c>
@@ -14369,7 +14365,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A332" s="14">
         <v>201802270796</v>
       </c>
@@ -14394,7 +14390,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A333" s="14">
         <v>201802270676</v>
       </c>
@@ -14419,7 +14415,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A334" s="14">
         <v>201802230375</v>
       </c>
@@ -14446,7 +14442,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A335" s="14">
         <v>201802260459</v>
       </c>
@@ -14475,7 +14471,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A336" s="14">
         <v>201802270941</v>
       </c>
@@ -14500,7 +14496,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A337" s="14">
         <v>201802270926</v>
       </c>
@@ -14525,7 +14521,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A338" s="14">
         <v>201802270755</v>
       </c>
@@ -14550,7 +14546,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A339" s="14">
         <v>201802260601</v>
       </c>
@@ -14575,7 +14571,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A340" s="14">
         <v>201802230278</v>
       </c>
@@ -14602,7 +14598,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A341" s="14">
         <v>201802260597</v>
       </c>
@@ -14627,7 +14623,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A342" s="14">
         <v>201802271024</v>
       </c>
@@ -14652,7 +14648,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A343" s="14">
         <v>201802270911</v>
       </c>
@@ -14677,7 +14673,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A344" s="14">
         <v>201802260509</v>
       </c>
@@ -14702,7 +14698,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A345" s="14">
         <v>201802240380</v>
       </c>
@@ -14729,7 +14725,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A346" s="14">
         <v>201802240383</v>
       </c>
@@ -14756,7 +14752,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A347" s="14">
         <v>201802260449</v>
       </c>
@@ -14783,7 +14779,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A348" s="14">
         <v>201802270692</v>
       </c>
@@ -14808,7 +14804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A349" s="14">
         <v>201802260575</v>
       </c>
@@ -14835,7 +14831,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A350" s="14">
         <v>201802270694</v>
       </c>
@@ -14860,7 +14856,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A351" s="14">
         <v>201802260622</v>
       </c>
@@ -14885,7 +14881,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A352" s="14">
         <v>201802270681</v>
       </c>
@@ -14912,7 +14908,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A353" s="14">
         <v>201802270677</v>
       </c>
@@ -14937,7 +14933,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A354" s="14">
         <v>201802270812</v>
       </c>
@@ -14962,7 +14958,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A355" s="14">
         <v>201802260447</v>
       </c>
@@ -14987,7 +14983,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A356" s="14">
         <v>201802230275</v>
       </c>
@@ -15012,7 +15008,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A357" s="14">
         <v>201802270915</v>
       </c>
@@ -15037,7 +15033,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A358" s="14">
         <v>201802230284</v>
       </c>
@@ -15062,7 +15058,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A359" s="14">
         <v>201802270773</v>
       </c>
@@ -15087,7 +15083,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A360" s="14">
         <v>201802271026</v>
       </c>
@@ -15114,7 +15110,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A361" s="14">
         <v>201802220239</v>
       </c>
@@ -15141,7 +15137,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A362" s="14">
         <v>201802270922</v>
       </c>
@@ -15166,7 +15162,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A363" s="14">
         <v>201802270869</v>
       </c>
@@ -15195,7 +15191,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A364" s="14">
         <v>201802270909</v>
       </c>
@@ -15220,7 +15216,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A365" s="14">
         <v>201802260591</v>
       </c>
@@ -15249,7 +15245,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A366" s="14">
         <v>201802270919</v>
       </c>
@@ -15274,7 +15270,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A367" s="14">
         <v>201802260611</v>
       </c>
@@ -15299,7 +15295,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A368" s="14">
         <v>201802271000</v>
       </c>
@@ -15324,7 +15320,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A369" s="14">
         <v>201802271056</v>
       </c>
@@ -15351,7 +15347,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A370" s="14">
         <v>201802220234</v>
       </c>
@@ -15376,7 +15372,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A371" s="14">
         <v>201802260456</v>
       </c>
@@ -15403,7 +15399,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A372" s="14">
         <v>201802270813</v>
       </c>
@@ -15428,7 +15424,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A373" s="14">
         <v>201802260479</v>
       </c>
@@ -15453,7 +15449,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A374" s="14">
         <v>201802271054</v>
       </c>
@@ -15480,7 +15476,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A375" s="14">
         <v>201802270768</v>
       </c>
@@ -15507,7 +15503,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A376" s="14">
         <v>201802260579</v>
       </c>
@@ -15534,7 +15530,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A377" s="14">
         <v>201802260505</v>
       </c>
@@ -15559,7 +15555,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A378" s="14">
         <v>201802230365</v>
       </c>
@@ -15586,7 +15582,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A379" s="14">
         <v>201802271046</v>
       </c>
@@ -15613,7 +15609,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A380" s="14">
         <v>201802270906</v>
       </c>
@@ -15638,7 +15634,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A381" s="14">
         <v>201802260424</v>
       </c>
@@ -15665,7 +15661,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A382" s="14">
         <v>201801319759</v>
       </c>
@@ -15692,7 +15688,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A383" s="14">
         <v>201802200098</v>
       </c>
@@ -15717,7 +15713,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A384" s="14">
         <v>201802260566</v>
       </c>
@@ -15742,7 +15738,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A385" s="14">
         <v>201802270730</v>
       </c>
@@ -15767,7 +15763,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A386" s="14">
         <v>201802270770</v>
       </c>
@@ -15792,7 +15788,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A387" s="14">
         <v>201802270745</v>
       </c>
@@ -15819,7 +15815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A388" s="14">
         <v>201802260614</v>
       </c>
@@ -15846,7 +15842,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A389" s="14">
         <v>201802270781</v>
       </c>
@@ -15871,7 +15867,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A390" s="14">
         <v>201802019767</v>
       </c>
@@ -15898,7 +15894,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A391" s="14">
         <v>201802270958</v>
       </c>
@@ -15923,7 +15919,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A392" s="14">
         <v>201802271004</v>
       </c>
@@ -15948,7 +15944,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A393" s="14">
         <v>201802271011</v>
       </c>
@@ -15977,7 +15973,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A394" s="14">
         <v>201802271016</v>
       </c>
@@ -16002,7 +15998,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A395" s="14">
         <v>201802270849</v>
       </c>
@@ -16029,7 +16025,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A396" s="14">
         <v>201802270829</v>
       </c>
@@ -16056,7 +16052,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A397" s="14">
         <v>201802260603</v>
       </c>
@@ -16081,7 +16077,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A398" s="14">
         <v>201802230283</v>
       </c>
@@ -16106,7 +16102,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A399" s="14">
         <v>201802270701</v>
       </c>
@@ -16131,7 +16127,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A400" s="14">
         <v>201802270859</v>
       </c>
@@ -16158,7 +16154,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A401" s="14">
         <v>201802260445</v>
       </c>
@@ -16185,7 +16181,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A402" s="14">
         <v>201802270874</v>
       </c>
@@ -16210,7 +16206,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A403" s="14">
         <v>201802270867</v>
       </c>
@@ -16235,7 +16231,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A404" s="14">
         <v>201802270939</v>
       </c>
@@ -16260,7 +16256,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A405" s="14">
         <v>201802260592</v>
       </c>
@@ -16287,7 +16283,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A406" s="14">
         <v>201802260619</v>
       </c>
@@ -16312,7 +16308,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A407" s="14">
         <v>201802270949</v>
       </c>
@@ -16337,7 +16333,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A408" s="14">
         <v>201802210139</v>
       </c>
@@ -16364,7 +16360,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A409" s="14">
         <v>201802230355</v>
       </c>
@@ -16391,7 +16387,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A410" s="14">
         <v>201802230372</v>
       </c>
@@ -16416,7 +16412,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A411" s="14">
         <v>201802230347</v>
       </c>
@@ -16441,7 +16437,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A412" s="14">
         <v>201802270948</v>
       </c>
@@ -16466,7 +16462,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A413" s="14">
         <v>201802270995</v>
       </c>
@@ -16491,7 +16487,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A414" s="14">
         <v>201802271010</v>
       </c>
@@ -16516,7 +16512,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A415" s="14">
         <v>201802260409</v>
       </c>
@@ -16541,7 +16537,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A416" s="14">
         <v>201802260589</v>
       </c>
@@ -16568,7 +16564,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A417" s="14">
         <v>201802260476</v>
       </c>
@@ -16593,7 +16589,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A418" s="14">
         <v>201802230346</v>
       </c>
@@ -16618,7 +16614,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A419" s="14">
         <v>201802260519</v>
       </c>
@@ -16643,7 +16639,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A420" s="14">
         <v>201802260473</v>
       </c>
@@ -16670,7 +16666,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A421" s="14">
         <v>201802270946</v>
       </c>
@@ -16695,7 +16691,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A422" s="14">
         <v>201802260570</v>
       </c>
@@ -16720,7 +16716,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A423" s="14">
         <v>201802270969</v>
       </c>
@@ -16745,7 +16741,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A424" s="14">
         <v>201802260582</v>
       </c>
@@ -16770,7 +16766,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A425" s="14">
         <v>201802270900</v>
       </c>
@@ -16795,7 +16791,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A426" s="14">
         <v>201802160041</v>
       </c>
@@ -16820,7 +16816,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A427" s="14">
         <v>201802160034</v>
       </c>
@@ -16845,7 +16841,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A428" s="14">
         <v>201802160039</v>
       </c>
@@ -16870,7 +16866,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A429" s="14">
         <v>201802160038</v>
       </c>
@@ -16895,7 +16891,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A430" s="14">
         <v>201802270674</v>
       </c>
@@ -16920,7 +16916,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A431" s="14">
         <v>201802270998</v>
       </c>
@@ -16945,7 +16941,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A432" s="14">
         <v>201802230320</v>
       </c>
@@ -16972,7 +16968,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A433" s="14">
         <v>201802210152</v>
       </c>
@@ -16999,7 +16995,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A434" s="14">
         <v>201802270791</v>
       </c>
@@ -17026,7 +17022,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A435" s="14">
         <v>201802170045</v>
       </c>
@@ -17053,7 +17049,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A436" s="14">
         <v>201802271018</v>
       </c>
@@ -17078,7 +17074,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A437" s="14">
         <v>201802220241</v>
       </c>
@@ -17103,7 +17099,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A438" s="14">
         <v>201802270810</v>
       </c>
@@ -17130,7 +17126,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A439" s="14">
         <v>201802270851</v>
       </c>
@@ -17157,7 +17153,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A440" s="14">
         <v>201802270630</v>
       </c>
@@ -17182,7 +17178,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A441" s="14">
         <v>201802270903</v>
       </c>
@@ -17207,7 +17203,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A442" s="14">
         <v>201802230376</v>
       </c>
@@ -17234,7 +17230,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A443" s="14">
         <v>201802270953</v>
       </c>
@@ -17259,7 +17255,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A444" s="14">
         <v>201802270809</v>
       </c>
@@ -17284,7 +17280,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A445" s="14">
         <v>201802260599</v>
       </c>
@@ -17311,7 +17307,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A446" s="14">
         <v>201802220220</v>
       </c>
@@ -17338,7 +17334,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A447" s="14">
         <v>201802270785</v>
       </c>
@@ -17363,7 +17359,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A448" s="14">
         <v>201802260629</v>
       </c>
@@ -17388,7 +17384,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A449" s="14">
         <v>201802270780</v>
       </c>
@@ -17415,7 +17411,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A450" s="14">
         <v>201802270828</v>
       </c>
@@ -17440,7 +17436,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A451" s="14">
         <v>201802270743</v>
       </c>
@@ -17465,7 +17461,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A452" s="14">
         <v>201802270837</v>
       </c>
@@ -17490,7 +17486,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A453" s="14">
         <v>201802260539</v>
       </c>
@@ -17515,7 +17511,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A454" s="14">
         <v>201802260609</v>
       </c>
@@ -17540,7 +17536,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A455" s="14">
         <v>201802149972</v>
       </c>
@@ -17567,7 +17563,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A456" s="14">
         <v>201802270786</v>
       </c>
@@ -17592,7 +17588,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A457" s="14">
         <v>201802230262</v>
       </c>
@@ -17617,7 +17613,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A458" s="14">
         <v>201802270924</v>
       </c>
@@ -17646,7 +17642,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A459" s="14">
         <v>201802150001</v>
       </c>
@@ -17673,7 +17669,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A460" s="14">
         <v>201802271036</v>
       </c>
@@ -17700,7 +17696,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A461" s="14">
         <v>201802270738</v>
       </c>
@@ -17725,7 +17721,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A462" s="14">
         <v>201802230367</v>
       </c>
@@ -17752,7 +17748,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A463" s="14">
         <v>201802200070</v>
       </c>
@@ -17779,7 +17775,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A464" s="14">
         <v>201802270723</v>
       </c>
@@ -17804,7 +17800,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A465" s="14">
         <v>201802270853</v>
       </c>
@@ -17831,7 +17827,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A466" s="14">
         <v>201802270779</v>
       </c>
@@ -17856,7 +17852,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A467" s="14">
         <v>201802230335</v>
       </c>
@@ -17881,7 +17877,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A468" s="14">
         <v>201802270720</v>
       </c>
@@ -17908,7 +17904,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A469" s="14">
         <v>201802260548</v>
       </c>
@@ -17933,7 +17929,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A470" s="14">
         <v>201802270918</v>
       </c>
@@ -17960,7 +17956,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A471" s="14">
         <v>201802270818</v>
       </c>
@@ -17985,7 +17981,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A472" s="14">
         <v>201802230249</v>
       </c>
@@ -18010,7 +18006,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A473" s="14">
         <v>201802270753</v>
       </c>
@@ -18039,7 +18035,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A474" s="14">
         <v>201802260578</v>
       </c>
@@ -18064,7 +18060,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A475" s="14">
         <v>201802270800</v>
       </c>
@@ -18089,7 +18085,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A476" s="14">
         <v>201802260605</v>
       </c>
@@ -18114,7 +18110,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A477" s="14">
         <v>201802270989</v>
       </c>
@@ -18139,7 +18135,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A478" s="14">
         <v>201802270807</v>
       </c>
@@ -18166,7 +18162,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A479" s="14">
         <v>201802270695</v>
       </c>
@@ -18191,7 +18187,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A480" s="14">
         <v>201802270884</v>
       </c>
@@ -18216,7 +18212,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A481" s="14">
         <v>201802270942</v>
       </c>
@@ -18243,7 +18239,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A482" s="14">
         <v>201802271020</v>
       </c>
@@ -18270,7 +18266,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A483" s="14">
         <v>201802270803</v>
       </c>
@@ -18295,7 +18291,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A484" s="14">
         <v>201802150009</v>
       </c>
@@ -18320,7 +18316,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A485" s="14">
         <v>201802150020</v>
       </c>
@@ -18345,7 +18341,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A486" s="14">
         <v>201802270749</v>
       </c>
@@ -18370,7 +18366,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A487" s="14">
         <v>201802270840</v>
       </c>
@@ -18397,7 +18393,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A488" s="14">
         <v>201802270761</v>
       </c>
@@ -18424,7 +18420,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A489" s="14">
         <v>201802270833</v>
       </c>
@@ -18449,7 +18445,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A490" s="14">
         <v>201802270634</v>
       </c>
@@ -18476,7 +18472,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A491" s="14">
         <v>201802270848</v>
       </c>
@@ -18501,7 +18497,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A492" s="14">
         <v>201802260593</v>
       </c>
@@ -18528,7 +18524,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A493" s="14">
         <v>201802230301</v>
       </c>
@@ -18553,7 +18549,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A494" s="14">
         <v>201802270959</v>
       </c>
@@ -18578,7 +18574,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A495" s="14">
         <v>201802271023</v>
       </c>
@@ -18607,7 +18603,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A496" s="14">
         <v>201802230270</v>
       </c>
@@ -18632,7 +18628,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A497" s="14">
         <v>201802260547</v>
       </c>
@@ -18657,7 +18653,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A498" s="14">
         <v>201802270930</v>
       </c>
@@ -18682,7 +18678,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A499" s="14">
         <v>201802260495</v>
       </c>
@@ -18709,7 +18705,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A500" s="14">
         <v>201802260486</v>
       </c>
@@ -18736,7 +18732,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" s="19"/>
       <c r="B501" s="19"/>
       <c r="C501" s="20"/>
@@ -18747,7 +18743,7 @@
       <c r="H501" s="21"/>
       <c r="I501" s="20"/>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" s="19"/>
       <c r="B502" s="19"/>
       <c r="C502" s="20"/>
@@ -18758,7 +18754,7 @@
       <c r="H502" s="24"/>
       <c r="I502" s="20"/>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" s="19"/>
       <c r="B503" s="19"/>
       <c r="C503" s="20"/>
@@ -18769,7 +18765,7 @@
       <c r="H503" s="25"/>
       <c r="I503" s="20"/>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" s="19"/>
       <c r="B504" s="19"/>
       <c r="C504" s="20"/>
@@ -18780,7 +18776,7 @@
       <c r="H504" s="24"/>
       <c r="I504" s="20"/>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" s="19"/>
       <c r="B505" s="19"/>
       <c r="C505" s="20"/>
@@ -18791,7 +18787,7 @@
       <c r="H505" s="27"/>
       <c r="I505" s="20"/>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" s="19"/>
       <c r="B506" s="19"/>
       <c r="C506" s="20"/>
@@ -18802,7 +18798,7 @@
       <c r="H506" s="28"/>
       <c r="I506" s="20"/>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" s="19"/>
       <c r="B507" s="19"/>
       <c r="C507" s="20"/>
@@ -18824,21 +18820,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18999,19 +18995,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F01EB60-9E6E-4945-BD45-C115F4651181}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25032AF2-00E2-40B4-AA38-5DE96A94CF47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F01EB60-9E6E-4945-BD45-C115F4651181}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
